--- a/docs/auditoria/ronda3/brian-documentos/fixtures/sintetico.xlsx
+++ b/docs/auditoria/ronda3/brian-documentos/fixtures/sintetico.xlsx
@@ -665,7 +665,6 @@
       <c r="G6" s="2">
         <f>ROUND(C6*1.07,2)</f>
         <v>160.49</v>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -720,7 +719,6 @@
       <c r="G8" s="2">
         <f>ROUND(C8*1.07,2)</f>
         <v>353.09</v>
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -790,7 +788,6 @@
       <c r="G11" s="2">
         <f>ROUND(C11*1.07,2)</f>
         <v>10.7</v>
-        <v/>
       </c>
     </row>
     <row r="14">
